--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -94,19 +94,19 @@
     <x:t>Initial Document Instructions Issued</x:t>
   </x:si>
   <x:si>
-    <x:t>24/03/23</x:t>
+    <x:t>24/05/23</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
   </x:si>
   <x:si>
-    <x:t>109</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09/03/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+    <x:t>145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22/05/23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>False</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -97,13 +97,13 @@
     <x:t>24/05/23</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>145</x:t>
   </x:si>
   <x:si>
-    <x:t>22/05/23</x:t>
+    <x:t>25/05/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -103,7 +103,7 @@
     <x:t>145</x:t>
   </x:si>
   <x:si>
-    <x:t>25/05/23</x:t>
+    <x:t>26/05/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
-    <x:t>145</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26/05/23</x:t>
+    <x:t>151</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/06/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>164</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12/07/23</x:t>
+    <x:t>168</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03/08/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
@@ -112,7 +112,7 @@
     <x:t>False</x:t>
   </x:si>
   <x:si>
-    <x:t>19/07/23</x:t>
+    <x:t>27/07/23</x:t>
   </x:si>
   <x:si>
     <x:t>28/02/23</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -97,13 +97,13 @@
     <x:t>24/12/23</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>168</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03/08/23</x:t>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/09/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>176</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/09/23</x:t>
+    <x:t>189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27/09/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27/09/23</x:t>
+    <x:t>199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05/10/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>199</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05/10/23</x:t>
+    <x:t>209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16/12/23</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>209</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16/12/23</x:t>
+    <x:t>215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11/01/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -97,13 +97,13 @@
     <x:t>24/12/23</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>215</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11/01/24</x:t>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>220</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30/01/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
@@ -593,7 +593,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>29</x:v>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>220</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30/01/24</x:t>
+    <x:t>222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/02/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
@@ -593,7 +593,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>29</x:v>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -100,10 +100,10 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>222</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01/02/24</x:t>
+    <x:t>225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10/02/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -94,16 +94,16 @@
     <x:t>Initial Document Instructions Issued</x:t>
   </x:si>
   <x:si>
-    <x:t>24/12/23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>225</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10/02/24</x:t>
+    <x:t>24/12/24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/02/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -85,7 +85,7 @@
     <x:t>sufi cup</x:t>
   </x:si>
   <x:si>
-    <x:t>27/02/23</x:t>
+    <x:t>23/02/23</x:t>
   </x:si>
   <x:si>
     <x:t>Green Visa1</x:t>
@@ -97,13 +97,13 @@
     <x:t>24/12/24</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>232</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21/02/24</x:t>
+    <x:t>40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15/03/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -61,7 +61,7 @@
     <x:t>Paid</x:t>
   </x:si>
   <x:si>
-    <x:t>Current NewZealand Visa Expiry</x:t>
+    <x:t>Current Visa Expiry</x:t>
   </x:si>
   <x:si>
     <x:t>Medical Issue Date</x:t>
@@ -97,13 +97,13 @@
     <x:t>24/12/24</x:t>
   </x:si>
   <x:si>
-    <x:t>40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>262</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15/03/24</x:t>
+    <x:t>42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>268</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/05/24</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
@@ -200,7 +200,7 @@
     <x:tableColumn id="13" name="Client Tags"/>
     <x:tableColumn id="14" name="Case Priority"/>
     <x:tableColumn id="15" name="Paid"/>
-    <x:tableColumn id="16" name="Current NewZealand Visa Expiry"/>
+    <x:tableColumn id="16" name="Current Visa Expiry"/>
     <x:tableColumn id="17" name="Medical Issue Date"/>
     <x:tableColumn id="18" name="Xray Issue Date"/>
     <x:tableColumn id="19" name="Police Certificate"/>

--- a/cypress/downloads/Client_Summary.xlsx
+++ b/cypress/downloads/Client_Summary.xlsx
@@ -97,13 +97,13 @@
     <x:t>24/12/24</x:t>
   </x:si>
   <x:si>
-    <x:t>42</x:t>
-  </x:si>
-  <x:si>
-    <x:t>268</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06/05/24</x:t>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>298</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28/03/25</x:t>
   </x:si>
   <x:si>
     <x:t>Owner nabeel</x:t>
